--- a/nriss-patch-1/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:05:55+00:00</t>
+    <t>2026-10-07T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
